--- a/Solutions/solution_models_RE46.xlsx
+++ b/Solutions/solution_models_RE46.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hans\box.fu\Thermolab\2022\v_22_03_23\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="S:\Thermolab\Github\Solutions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4DA1745-3155-440E-AA3F-B087E36E53F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB6C6783-213E-4D50-8AB8-6DC71B32A44B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3420" yWindow="3420" windowWidth="28800" windowHeight="15540" activeTab="2" xr2:uid="{E063EFA9-EFF7-41CC-8A99-CB5ABE164D42}"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="4" xr2:uid="{E063EFA9-EFF7-41CC-8A99-CB5ABE164D42}"/>
   </bookViews>
   <sheets>
     <sheet name="Ilmenite" sheetId="3" r:id="rId1"/>
@@ -32,6 +32,9 @@
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -691,12 +694,12 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{49443980-1F64-47E7-A56F-298C26DE6016}">
   <sheetPr codeName="Sheet9"/>
   <dimension ref="A1:E22"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.453125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -704,7 +707,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -721,7 +724,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -738,7 +741,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>25</v>
       </c>
@@ -755,7 +758,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>26</v>
       </c>
@@ -772,7 +775,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>12</v>
       </c>
@@ -789,7 +792,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>13</v>
       </c>
@@ -806,7 +809,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>14</v>
       </c>
@@ -823,7 +826,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>15</v>
       </c>
@@ -832,7 +835,7 @@
         <v>6.6666666666666666E-2</v>
       </c>
       <c r="C13">
-        <f t="shared" ref="C13:F13" si="0">1/15</f>
+        <f t="shared" ref="C13:E13" si="0">1/15</f>
         <v>6.6666666666666666E-2</v>
       </c>
       <c r="D13">
@@ -844,7 +847,7 @@
         <v>6.6666666666666666E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>16</v>
       </c>
@@ -861,7 +864,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>17</v>
       </c>
@@ -872,7 +875,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>27</v>
       </c>
@@ -884,7 +887,7 @@
       </c>
       <c r="D17" s="2"/>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>28</v>
       </c>
@@ -896,10 +899,10 @@
       </c>
       <c r="D18" s="2"/>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="D20" s="2"/>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B22" s="2"/>
     </row>
   </sheetData>
@@ -911,9 +914,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{16DE0FFC-32FF-4CEA-8C88-64C62D24FB94}">
   <sheetPr codeName="Sheet5"/>
   <dimension ref="A1:J31"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -921,7 +924,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -932,7 +935,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -943,7 +946,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>53</v>
       </c>
@@ -954,7 +957,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>54</v>
       </c>
@@ -965,7 +968,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>12</v>
       </c>
@@ -976,7 +979,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>13</v>
       </c>
@@ -987,7 +990,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>14</v>
       </c>
@@ -998,7 +1001,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>15</v>
       </c>
@@ -1011,7 +1014,7 @@
         <v>6.6666666666666666E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>16</v>
       </c>
@@ -1022,7 +1025,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>17</v>
       </c>
@@ -1033,7 +1036,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>55</v>
       </c>
@@ -1047,7 +1050,7 @@
       <c r="I17" s="2"/>
       <c r="J17" s="2"/>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>56</v>
       </c>
@@ -1061,7 +1064,7 @@
       <c r="H18" s="2"/>
       <c r="J18" s="2"/>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>41</v>
       </c>
@@ -1072,7 +1075,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>55</v>
       </c>
@@ -1083,7 +1086,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>56</v>
       </c>
@@ -1094,7 +1097,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>40</v>
       </c>
@@ -1105,7 +1108,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>55</v>
       </c>
@@ -1118,7 +1121,7 @@
       <c r="D25" s="2"/>
       <c r="J25" s="2"/>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>56</v>
       </c>
@@ -1129,7 +1132,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>39</v>
       </c>
@@ -1140,7 +1143,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>31</v>
       </c>
@@ -1151,7 +1154,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>30</v>
       </c>
@@ -1162,7 +1165,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>29</v>
       </c>
@@ -1182,12 +1185,12 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A121636C-ACA9-4165-99DA-60F3507CFB62}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:R67"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.453125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1195,7 +1198,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -1251,7 +1254,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -1307,7 +1310,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>77</v>
       </c>
@@ -1363,7 +1366,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>78</v>
       </c>
@@ -1419,7 +1422,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>79</v>
       </c>
@@ -1475,7 +1478,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>80</v>
       </c>
@@ -1531,7 +1534,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>81</v>
       </c>
@@ -1587,7 +1590,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>82</v>
       </c>
@@ -1643,7 +1646,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>83</v>
       </c>
@@ -1699,7 +1702,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>84</v>
       </c>
@@ -1755,7 +1758,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>85</v>
       </c>
@@ -1811,7 +1814,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>86</v>
       </c>
@@ -1867,7 +1870,7 @@
         <v>1.8</v>
       </c>
     </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>87</v>
       </c>
@@ -1923,7 +1926,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>12</v>
       </c>
@@ -1979,7 +1982,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>13</v>
       </c>
@@ -2035,7 +2038,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>14</v>
       </c>
@@ -2055,7 +2058,7 @@
         <v>1</v>
       </c>
       <c r="G21">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="H21">
         <v>1</v>
@@ -2091,7 +2094,7 @@
         <v>1.8</v>
       </c>
     </row>
-    <row r="22" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>15</v>
       </c>
@@ -2164,7 +2167,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="23" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>16</v>
       </c>
@@ -2220,7 +2223,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>17</v>
       </c>
@@ -2258,7 +2261,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="26" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>88</v>
       </c>
@@ -2296,7 +2299,7 @@
         <v>17800</v>
       </c>
     </row>
-    <row r="27" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>89</v>
       </c>
@@ -2334,7 +2337,7 @@
         <v>23700</v>
       </c>
     </row>
-    <row r="28" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>90</v>
       </c>
@@ -2372,7 +2375,7 @@
         <v>40300</v>
       </c>
     </row>
-    <row r="29" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>91</v>
       </c>
@@ -2410,7 +2413,7 @@
         <v>9400</v>
       </c>
     </row>
-    <row r="30" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>92</v>
       </c>
@@ -2448,7 +2451,7 @@
         <v>9200</v>
       </c>
     </row>
-    <row r="31" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>93</v>
       </c>
@@ -2486,7 +2489,7 @@
         <v>-8300</v>
       </c>
     </row>
-    <row r="32" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>94</v>
       </c>
@@ -2524,7 +2527,7 @@
         <v>30000</v>
       </c>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>95</v>
       </c>
@@ -2562,7 +2565,7 @@
         <v>30000</v>
       </c>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>96</v>
       </c>
@@ -2600,7 +2603,7 @@
         <v>-100</v>
       </c>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>97</v>
       </c>
@@ -2638,7 +2641,7 @@
         <v>17300</v>
       </c>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>98</v>
       </c>
@@ -2676,7 +2679,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>41</v>
       </c>
@@ -2714,7 +2717,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>88</v>
       </c>
@@ -2752,7 +2755,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>89</v>
       </c>
@@ -2790,7 +2793,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>90</v>
       </c>
@@ -2828,7 +2831,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>91</v>
       </c>
@@ -2866,7 +2869,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>92</v>
       </c>
@@ -2904,7 +2907,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>93</v>
       </c>
@@ -2942,7 +2945,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>94</v>
       </c>
@@ -2980,7 +2983,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>95</v>
       </c>
@@ -3018,7 +3021,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>96</v>
       </c>
@@ -3056,7 +3059,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>97</v>
       </c>
@@ -3094,7 +3097,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>98</v>
       </c>
@@ -3132,7 +3135,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>40</v>
       </c>
@@ -3170,7 +3173,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>88</v>
       </c>
@@ -3208,7 +3211,7 @@
         <v>-610</v>
       </c>
     </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>89</v>
       </c>
@@ -3246,7 +3249,7 @@
         <v>-940</v>
       </c>
     </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>90</v>
       </c>
@@ -3284,7 +3287,7 @@
         <v>-860</v>
       </c>
     </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>91</v>
       </c>
@@ -3322,7 +3325,7 @@
         <v>-1580</v>
       </c>
     </row>
-    <row r="56" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>92</v>
       </c>
@@ -3360,7 +3363,7 @@
         <v>-1580</v>
       </c>
     </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>93</v>
       </c>
@@ -3398,7 +3401,7 @@
         <v>-60</v>
       </c>
     </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>94</v>
       </c>
@@ -3436,7 +3439,7 @@
         <v>-660</v>
       </c>
     </row>
-    <row r="59" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>95</v>
       </c>
@@ -3474,7 +3477,7 @@
         <v>-600</v>
       </c>
     </row>
-    <row r="60" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>96</v>
       </c>
@@ -3512,7 +3515,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="61" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>97</v>
       </c>
@@ -3550,7 +3553,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="62" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>98</v>
       </c>
@@ -3588,7 +3591,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>39</v>
       </c>
@@ -3626,7 +3629,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="65" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>31</v>
       </c>
@@ -3664,7 +3667,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="66" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>30</v>
       </c>
@@ -3702,7 +3705,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>29</v>
       </c>
@@ -3749,12 +3752,12 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{56080F09-1E90-4ABB-8E91-2CFD7037624D}">
   <sheetPr codeName="Sheet13"/>
   <dimension ref="A1:P99"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="14" width="8.54296875" customWidth="1"/>
+    <col min="2" max="14" width="8.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -3762,7 +3765,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -3797,7 +3800,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -3832,7 +3835,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>48</v>
       </c>
@@ -3867,7 +3870,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>47</v>
       </c>
@@ -3902,7 +3905,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>46</v>
       </c>
@@ -3937,7 +3940,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>45</v>
       </c>
@@ -3972,7 +3975,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>44</v>
       </c>
@@ -4007,7 +4010,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>43</v>
       </c>
@@ -4042,7 +4045,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>42</v>
       </c>
@@ -4077,7 +4080,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
       <c r="D13" s="1"/>
@@ -4089,7 +4092,7 @@
       <c r="J13" s="1"/>
       <c r="K13" s="1"/>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>12</v>
       </c>
@@ -4124,7 +4127,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>13</v>
       </c>
@@ -4159,12 +4162,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>14</v>
       </c>
       <c r="B17">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="C17">
         <v>1</v>
@@ -4185,7 +4188,7 @@
         <v>1</v>
       </c>
       <c r="I17">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="J17">
         <v>1</v>
@@ -4194,7 +4197,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>15</v>
       </c>
@@ -4239,7 +4242,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>16</v>
       </c>
@@ -4274,7 +4277,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>17</v>
       </c>
@@ -4300,7 +4303,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>38</v>
       </c>
@@ -4326,7 +4329,7 @@
         <v>20600</v>
       </c>
     </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>37</v>
       </c>
@@ -4353,7 +4356,7 @@
       </c>
       <c r="I23" s="1"/>
     </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>36</v>
       </c>
@@ -4380,7 +4383,7 @@
       </c>
       <c r="I24" s="1"/>
     </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>35</v>
       </c>
@@ -4409,7 +4412,7 @@
       <c r="M25" s="1"/>
       <c r="N25" s="1"/>
     </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>34</v>
       </c>
@@ -4438,7 +4441,7 @@
       <c r="M26" s="1"/>
       <c r="N26" s="1"/>
     </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>33</v>
       </c>
@@ -4470,7 +4473,7 @@
       <c r="M27" s="1"/>
       <c r="N27" s="1"/>
     </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>32</v>
       </c>
@@ -4502,14 +4505,14 @@
       <c r="M28" s="1"/>
       <c r="N28" s="1"/>
     </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="J29" s="1"/>
       <c r="K29" s="1"/>
       <c r="L29" s="1"/>
       <c r="M29" s="1"/>
       <c r="N29" s="1"/>
     </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>41</v>
       </c>
@@ -4540,7 +4543,7 @@
       <c r="M30" s="1"/>
       <c r="N30" s="1"/>
     </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>38</v>
       </c>
@@ -4571,7 +4574,7 @@
       <c r="M31" s="1"/>
       <c r="N31" s="1"/>
     </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>37</v>
       </c>
@@ -4603,7 +4606,7 @@
       <c r="M32" s="1"/>
       <c r="N32" s="1"/>
     </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>36</v>
       </c>
@@ -4635,7 +4638,7 @@
       <c r="M33" s="1"/>
       <c r="N33" s="1"/>
     </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>35</v>
       </c>
@@ -4662,7 +4665,7 @@
       </c>
       <c r="I34" s="1"/>
     </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>34</v>
       </c>
@@ -4689,7 +4692,7 @@
       </c>
       <c r="I35" s="1"/>
     </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>33</v>
       </c>
@@ -4716,7 +4719,7 @@
       </c>
       <c r="I36" s="1"/>
     </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>32</v>
       </c>
@@ -4743,7 +4746,7 @@
       </c>
       <c r="I37" s="1"/>
     </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:14" x14ac:dyDescent="0.25">
       <c r="D38" s="1"/>
       <c r="E38" s="1"/>
       <c r="F38" s="1"/>
@@ -4751,7 +4754,7 @@
       <c r="H38" s="1"/>
       <c r="I38" s="1"/>
     </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>40</v>
       </c>
@@ -4777,7 +4780,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>38</v>
       </c>
@@ -4803,7 +4806,7 @@
         <v>-30</v>
       </c>
     </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>37</v>
       </c>
@@ -4830,7 +4833,7 @@
       </c>
       <c r="I41" s="1"/>
     </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>36</v>
       </c>
@@ -4857,7 +4860,7 @@
       </c>
       <c r="I42" s="1"/>
     </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>35</v>
       </c>
@@ -4884,7 +4887,7 @@
       </c>
       <c r="I43" s="1"/>
     </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>34</v>
       </c>
@@ -4911,7 +4914,7 @@
       </c>
       <c r="I44" s="1"/>
     </row>
-    <row r="45" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>33</v>
       </c>
@@ -4938,7 +4941,7 @@
       </c>
       <c r="I45" s="1"/>
     </row>
-    <row r="46" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>32</v>
       </c>
@@ -4965,7 +4968,7 @@
       </c>
       <c r="I46" s="1"/>
     </row>
-    <row r="48" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>39</v>
       </c>
@@ -4991,7 +4994,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>31</v>
       </c>
@@ -5018,7 +5021,7 @@
       </c>
       <c r="I49" s="1"/>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>30</v>
       </c>
@@ -5045,7 +5048,7 @@
       </c>
       <c r="I50" s="1"/>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>29</v>
       </c>
@@ -5072,7 +5075,7 @@
       </c>
       <c r="I51" s="1"/>
     </row>
-    <row r="86" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A86" s="1"/>
       <c r="B86" s="1"/>
       <c r="C86" s="1"/>
@@ -5090,7 +5093,7 @@
       <c r="O86" s="1"/>
       <c r="P86" s="1"/>
     </row>
-    <row r="87" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A87" s="1"/>
       <c r="B87" s="1"/>
       <c r="C87" s="1"/>
@@ -5108,7 +5111,7 @@
       <c r="O87" s="1"/>
       <c r="P87" s="1"/>
     </row>
-    <row r="88" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A88" s="1"/>
       <c r="B88" s="1"/>
       <c r="C88" s="1"/>
@@ -5126,7 +5129,7 @@
       <c r="O88" s="1"/>
       <c r="P88" s="1"/>
     </row>
-    <row r="89" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A89" s="1"/>
       <c r="B89" s="1"/>
       <c r="C89" s="1"/>
@@ -5144,7 +5147,7 @@
       <c r="O89" s="1"/>
       <c r="P89" s="1"/>
     </row>
-    <row r="90" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A90" s="1"/>
       <c r="B90" s="1"/>
       <c r="C90" s="1"/>
@@ -5162,7 +5165,7 @@
       <c r="O90" s="1"/>
       <c r="P90" s="1"/>
     </row>
-    <row r="91" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A91" s="1"/>
       <c r="B91" s="1"/>
       <c r="C91" s="1"/>
@@ -5180,7 +5183,7 @@
       <c r="O91" s="1"/>
       <c r="P91" s="1"/>
     </row>
-    <row r="92" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A92" s="1"/>
       <c r="B92" s="1"/>
       <c r="C92" s="1"/>
@@ -5198,7 +5201,7 @@
       <c r="O92" s="1"/>
       <c r="P92" s="1"/>
     </row>
-    <row r="93" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A93" s="1"/>
       <c r="B93" s="1"/>
       <c r="C93" s="1"/>
@@ -5216,7 +5219,7 @@
       <c r="O93" s="1"/>
       <c r="P93" s="1"/>
     </row>
-    <row r="94" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A94" s="1"/>
       <c r="B94" s="1"/>
       <c r="C94" s="1"/>
@@ -5234,7 +5237,7 @@
       <c r="O94" s="1"/>
       <c r="P94" s="1"/>
     </row>
-    <row r="95" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A95" s="1"/>
       <c r="B95" s="1"/>
       <c r="C95" s="1"/>
@@ -5252,7 +5255,7 @@
       <c r="O95" s="1"/>
       <c r="P95" s="1"/>
     </row>
-    <row r="96" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A96" s="1"/>
       <c r="B96" s="1"/>
       <c r="C96" s="1"/>
@@ -5270,7 +5273,7 @@
       <c r="O96" s="1"/>
       <c r="P96" s="1"/>
     </row>
-    <row r="97" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A97" s="1"/>
       <c r="B97" s="1"/>
       <c r="C97" s="1"/>
@@ -5288,7 +5291,7 @@
       <c r="O97" s="1"/>
       <c r="P97" s="1"/>
     </row>
-    <row r="98" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A98" s="1"/>
       <c r="B98" s="1"/>
       <c r="C98" s="1"/>
@@ -5306,7 +5309,7 @@
       <c r="O98" s="1"/>
       <c r="P98" s="1"/>
     </row>
-    <row r="99" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A99" s="1"/>
       <c r="B99" s="1"/>
       <c r="C99" s="1"/>
@@ -5333,9 +5336,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE74B3D5-457C-4022-81EF-26E0AA70A107}">
   <sheetPr codeName="Sheet8"/>
   <dimension ref="A1:F22"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -5343,7 +5346,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -5363,7 +5366,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -5383,7 +5386,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -5403,7 +5406,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -5423,7 +5426,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>10</v>
       </c>
@@ -5443,7 +5446,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>11</v>
       </c>
@@ -5463,7 +5466,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>12</v>
       </c>
@@ -5483,7 +5486,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>13</v>
       </c>
@@ -5503,7 +5506,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>14</v>
       </c>
@@ -5517,13 +5520,13 @@
         <v>1</v>
       </c>
       <c r="E14">
-        <v>0.3</v>
+        <v>1</v>
       </c>
       <c r="F14">
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>15</v>
       </c>
@@ -5548,7 +5551,7 @@
         <v>6.6666666666666666E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>16</v>
       </c>
@@ -5568,7 +5571,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>17</v>
       </c>
@@ -5585,7 +5588,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>18</v>
       </c>
@@ -5602,7 +5605,7 @@
         <v>24000</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>19</v>
       </c>
@@ -5619,7 +5622,7 @@
         <v>4500</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>20</v>
       </c>
@@ -5636,7 +5639,7 @@
         <v>4500</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>21</v>
       </c>
